--- a/assets/Gemini_Antigravity_Excel.xlsx
+++ b/assets/Gemini_Antigravity_Excel.xlsx
@@ -17,7 +17,7 @@
 
 <file path=xl/webextensions/webextension.xml><?xml version="1.0" encoding="utf-8"?>
 <we:webextension xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{7F89B2E3-8E5A-4B21-996A-12E4A9F200A1}">
-  <we:reference id="7F89B2E3-8E5A-4B21-996A-12E4A9F200A1" version="1.0.0.0" store="developer" storeType="Registry"/>
+  <we:reference id="7F89B2E3-8E5A-4B21-996A-12E4A9F200A1" version="1.0.1.0" store="developer" storeType="Registry"/>
   <we:alternateReferences/>
   <we:properties/>
   <we:bindings/>
